--- a/final_data_pipeline/output/311313_elec_options.xlsx
+++ b/final_data_pipeline/output/311313_elec_options.xlsx
@@ -1101,7 +1101,7 @@
         <v>172</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -1193,7 +1193,7 @@
         <v>172</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1291,7 +1291,7 @@
         <v>172</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1386,7 +1386,7 @@
         <v>172</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1475,7 +1475,7 @@
         <v>172</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1564,7 +1564,7 @@
         <v>172</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1659,7 +1659,7 @@
         <v>172</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1754,7 +1754,7 @@
         <v>172</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1849,7 +1849,7 @@
         <v>172</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1944,7 +1944,7 @@
         <v>172</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -2033,7 +2033,7 @@
         <v>172</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -2122,7 +2122,7 @@
         <v>172</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -2217,7 +2217,7 @@
         <v>172</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2315,7 +2315,7 @@
         <v>172</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2413,7 +2413,7 @@
         <v>172</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2505,7 +2505,7 @@
         <v>172</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2597,7 +2597,7 @@
         <v>172</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2695,7 +2695,7 @@
         <v>172</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2790,7 +2790,7 @@
         <v>172</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2879,7 +2879,7 @@
         <v>172</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2968,7 +2968,7 @@
         <v>172</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -3063,7 +3063,7 @@
         <v>172</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -3158,7 +3158,7 @@
         <v>172</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -3256,7 +3256,7 @@
         <v>172</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -3354,7 +3354,7 @@
         <v>172</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE26">
         <v>8000</v>
@@ -3455,7 +3455,7 @@
         <v>172</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE27">
         <v>8000</v>
@@ -3550,7 +3550,7 @@
         <v>173</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE28">
         <v>8000</v>
@@ -3639,7 +3639,7 @@
         <v>173</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE29">
         <v>8000</v>
@@ -3728,7 +3728,7 @@
         <v>173</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE30">
         <v>8000</v>
@@ -3823,7 +3823,7 @@
         <v>173</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE31">
         <v>8000</v>
@@ -3918,7 +3918,7 @@
         <v>173</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -5776,7 +5776,7 @@
         <v>172</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5865,7 +5865,7 @@
         <v>172</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5954,7 +5954,7 @@
         <v>172</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -6043,7 +6043,7 @@
         <v>172</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6135,7 +6135,7 @@
         <v>172</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6227,7 +6227,7 @@
         <v>172</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6316,7 +6316,7 @@
         <v>172</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6408,7 +6408,7 @@
         <v>172</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6500,7 +6500,7 @@
         <v>172</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6589,7 +6589,7 @@
         <v>172</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6678,7 +6678,7 @@
         <v>173</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6767,7 +6767,7 @@
         <v>173</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6856,7 +6856,7 @@
         <v>172</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -6945,7 +6945,7 @@
         <v>172</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -7034,7 +7034,7 @@
         <v>172</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -7126,7 +7126,7 @@
         <v>172</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -7218,7 +7218,7 @@
         <v>172</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE68">
         <v>8000</v>
@@ -7310,7 +7310,7 @@
         <v>172</v>
       </c>
       <c r="AD69">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE69">
         <v>8000</v>
@@ -7399,7 +7399,7 @@
         <v>172</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7488,7 +7488,7 @@
         <v>172</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7577,7 +7577,7 @@
         <v>172</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -7666,7 +7666,7 @@
         <v>172</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7755,7 +7755,7 @@
         <v>173</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -7844,7 +7844,7 @@
         <v>173</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -7936,7 +7936,7 @@
         <v>172</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -8025,7 +8025,7 @@
         <v>172</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -8120,7 +8120,7 @@
         <v>172</v>
       </c>
       <c r="AD78">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE78">
         <v>8000</v>
@@ -8209,7 +8209,7 @@
         <v>173</v>
       </c>
       <c r="AD79">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE79">
         <v>8000</v>
@@ -8304,7 +8304,7 @@
         <v>173</v>
       </c>
       <c r="AD80">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE80">
         <v>8000</v>
@@ -8393,7 +8393,7 @@
         <v>172</v>
       </c>
       <c r="AD81">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE81">
         <v>8000</v>
@@ -8488,7 +8488,7 @@
         <v>172</v>
       </c>
       <c r="AD82">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE82">
         <v>8000</v>
@@ -8577,7 +8577,7 @@
         <v>172</v>
       </c>
       <c r="AD83">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE83">
         <v>8000</v>
@@ -8666,7 +8666,7 @@
         <v>173</v>
       </c>
       <c r="AD84">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE84">
         <v>8000</v>
@@ -8758,7 +8758,7 @@
         <v>172</v>
       </c>
       <c r="AD85">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE85">
         <v>8000</v>
@@ -8856,7 +8856,7 @@
         <v>172</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE86">
         <v>8000</v>
@@ -8948,7 +8948,7 @@
         <v>172</v>
       </c>
       <c r="AD87">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE87">
         <v>8000</v>
@@ -9037,7 +9037,7 @@
         <v>172</v>
       </c>
       <c r="AD88">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE88">
         <v>8000</v>
@@ -9138,7 +9138,7 @@
         <v>172</v>
       </c>
       <c r="AD89">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE89">
         <v>8000</v>
@@ -9224,7 +9224,7 @@
         <v>18279.05718989691</v>
       </c>
       <c r="AD90">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE90">
         <v>8000</v>
@@ -9313,7 +9313,7 @@
         <v>172</v>
       </c>
       <c r="AD91">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE91">
         <v>8000</v>
@@ -9408,7 +9408,7 @@
         <v>172</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9497,7 +9497,7 @@
         <v>172</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9589,7 +9589,7 @@
         <v>172</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9687,7 +9687,7 @@
         <v>172</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9779,7 +9779,7 @@
         <v>172</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9874,7 +9874,7 @@
         <v>172</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -9963,7 +9963,7 @@
         <v>172</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -10058,7 +10058,7 @@
         <v>172</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -10153,7 +10153,7 @@
         <v>172</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -10242,7 +10242,7 @@
         <v>172</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -10337,7 +10337,7 @@
         <v>172</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -10435,7 +10435,7 @@
         <v>172</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10524,7 +10524,7 @@
         <v>173</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10619,7 +10619,7 @@
         <v>173</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -10714,7 +10714,7 @@
         <v>173</v>
       </c>
       <c r="AD106">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE106">
         <v>8000</v>
@@ -10812,7 +10812,7 @@
         <v>172</v>
       </c>
       <c r="AD107">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE107">
         <v>8000</v>
@@ -10904,7 +10904,7 @@
         <v>172</v>
       </c>
       <c r="AD108">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE108">
         <v>8000</v>
@@ -11002,7 +11002,7 @@
         <v>172</v>
       </c>
       <c r="AD109">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE109">
         <v>8000</v>
@@ -11094,7 +11094,7 @@
         <v>172</v>
       </c>
       <c r="AD110">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE110">
         <v>8000</v>
@@ -11192,7 +11192,7 @@
         <v>172</v>
       </c>
       <c r="AD111">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE111">
         <v>8000</v>
@@ -11293,7 +11293,7 @@
         <v>172</v>
       </c>
       <c r="AD112">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE112">
         <v>8000</v>
@@ -11388,7 +11388,7 @@
         <v>172</v>
       </c>
       <c r="AD113">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE113">
         <v>8000</v>
@@ -11477,7 +11477,7 @@
         <v>172</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE114">
         <v>8000</v>
@@ -11575,7 +11575,7 @@
         <v>172</v>
       </c>
       <c r="AD115">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE115">
         <v>8000</v>
@@ -11673,7 +11673,7 @@
         <v>172</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE116">
         <v>8000</v>
@@ -11765,7 +11765,7 @@
         <v>172</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -11860,7 +11860,7 @@
         <v>172</v>
       </c>
       <c r="AD118">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE118">
         <v>8000</v>
@@ -11952,7 +11952,7 @@
         <v>172</v>
       </c>
       <c r="AD119">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE119">
         <v>8000</v>
@@ -12041,7 +12041,7 @@
         <v>172</v>
       </c>
       <c r="AD120">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE120">
         <v>8000</v>
@@ -12133,7 +12133,7 @@
         <v>172</v>
       </c>
       <c r="AD121">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE121">
         <v>8000</v>
@@ -12225,7 +12225,7 @@
         <v>172</v>
       </c>
       <c r="AD122">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE122">
         <v>8000</v>
@@ -12314,7 +12314,7 @@
         <v>172</v>
       </c>
       <c r="AD123">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE123">
         <v>8000</v>
@@ -12406,7 +12406,7 @@
         <v>172</v>
       </c>
       <c r="AD124">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE124">
         <v>8000</v>
@@ -12498,7 +12498,7 @@
         <v>172</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12587,7 +12587,7 @@
         <v>172</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -12676,7 +12676,7 @@
         <v>172</v>
       </c>
       <c r="AD127">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE127">
         <v>8000</v>
@@ -12765,7 +12765,7 @@
         <v>172</v>
       </c>
       <c r="AD128">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE128">
         <v>8000</v>
@@ -12854,7 +12854,7 @@
         <v>172</v>
       </c>
       <c r="AD129">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE129">
         <v>8000</v>
@@ -12943,7 +12943,7 @@
         <v>172</v>
       </c>
       <c r="AD130">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE130">
         <v>8000</v>
@@ -13035,7 +13035,7 @@
         <v>172</v>
       </c>
       <c r="AD131">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE131">
         <v>8000</v>
@@ -13127,7 +13127,7 @@
         <v>172</v>
       </c>
       <c r="AD132">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE132">
         <v>8000</v>
@@ -13219,7 +13219,7 @@
         <v>172</v>
       </c>
       <c r="AD133">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE133">
         <v>8000</v>
@@ -13308,7 +13308,7 @@
         <v>173</v>
       </c>
       <c r="AD134">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE134">
         <v>8000</v>
@@ -13397,7 +13397,7 @@
         <v>173</v>
       </c>
       <c r="AD135">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE135">
         <v>8000</v>
@@ -13486,7 +13486,7 @@
         <v>172</v>
       </c>
       <c r="AD136">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE136">
         <v>8000</v>
@@ -13575,7 +13575,7 @@
         <v>172</v>
       </c>
       <c r="AD137">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE137">
         <v>8000</v>
@@ -13664,7 +13664,7 @@
         <v>173</v>
       </c>
       <c r="AD138">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE138">
         <v>8000</v>
@@ -13756,7 +13756,7 @@
         <v>172</v>
       </c>
       <c r="AD139">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AE139">
         <v>8000</v>
@@ -13848,7 +13848,7 @@
         <v>172</v>
       </c>
       <c r="AD140">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE140">
         <v>8000</v>
@@ -13940,7 +13940,7 @@
         <v>172</v>
       </c>
       <c r="AD141">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE141">
         <v>8000</v>
@@ -14032,7 +14032,7 @@
         <v>172</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -14121,7 +14121,7 @@
         <v>172</v>
       </c>
       <c r="AD143">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE143">
         <v>8000</v>
@@ -14210,7 +14210,7 @@
         <v>172</v>
       </c>
       <c r="AD144">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE144">
         <v>8000</v>
@@ -14299,7 +14299,7 @@
         <v>172</v>
       </c>
       <c r="AD145">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE145">
         <v>8000</v>
@@ -14391,7 +14391,7 @@
         <v>172</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -14480,7 +14480,7 @@
         <v>172</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -14572,7 +14572,7 @@
         <v>172</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -14661,7 +14661,7 @@
         <v>173</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -14750,7 +14750,7 @@
         <v>173</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -14839,7 +14839,7 @@
         <v>172</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -14928,7 +14928,7 @@
         <v>172</v>
       </c>
       <c r="AD152">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE152">
         <v>8000</v>
@@ -15020,7 +15020,7 @@
         <v>172</v>
       </c>
       <c r="AD153">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE153">
         <v>8000</v>
@@ -15109,7 +15109,7 @@
         <v>173</v>
       </c>
       <c r="AD154">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE154">
         <v>8000</v>
@@ -15198,7 +15198,7 @@
         <v>173</v>
       </c>
       <c r="AD155">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE155">
         <v>8000</v>
@@ -15290,7 +15290,7 @@
         <v>172</v>
       </c>
       <c r="AD156">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE156">
         <v>8000</v>
@@ -15382,7 +15382,7 @@
         <v>172</v>
       </c>
       <c r="AD157">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE157">
         <v>8000</v>
@@ -15471,7 +15471,7 @@
         <v>172</v>
       </c>
       <c r="AD158">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE158">
         <v>8000</v>
@@ -15560,7 +15560,7 @@
         <v>172</v>
       </c>
       <c r="AD159">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE159">
         <v>8000</v>
@@ -15652,7 +15652,7 @@
         <v>172</v>
       </c>
       <c r="AD160">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE160">
         <v>8000</v>
@@ -15744,7 +15744,7 @@
         <v>172</v>
       </c>
       <c r="AD161">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE161">
         <v>8000</v>
@@ -15833,7 +15833,7 @@
         <v>172</v>
       </c>
       <c r="AD162">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE162">
         <v>8000</v>
@@ -15922,7 +15922,7 @@
         <v>172</v>
       </c>
       <c r="AD163">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE163">
         <v>8000</v>
@@ -16011,7 +16011,7 @@
         <v>172</v>
       </c>
       <c r="AD164">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE164">
         <v>8000</v>
@@ -16100,7 +16100,7 @@
         <v>172</v>
       </c>
       <c r="AD165">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE165">
         <v>8000</v>
@@ -16192,7 +16192,7 @@
         <v>172</v>
       </c>
       <c r="AD166">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE166">
         <v>8000</v>
@@ -16284,7 +16284,7 @@
         <v>172</v>
       </c>
       <c r="AD167">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE167">
         <v>8000</v>
@@ -16382,7 +16382,7 @@
         <v>172</v>
       </c>
       <c r="AD168">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE168">
         <v>8000</v>
@@ -16480,7 +16480,7 @@
         <v>172</v>
       </c>
       <c r="AD169">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE169">
         <v>8000</v>
@@ -16572,7 +16572,7 @@
         <v>172</v>
       </c>
       <c r="AD170">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE170">
         <v>8000</v>
@@ -16664,7 +16664,7 @@
         <v>172</v>
       </c>
       <c r="AD171">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE171">
         <v>8000</v>
@@ -16756,7 +16756,7 @@
         <v>172</v>
       </c>
       <c r="AD172">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE172">
         <v>8000</v>
@@ -16848,7 +16848,7 @@
         <v>172</v>
       </c>
       <c r="AD173">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE173">
         <v>8000</v>
@@ -16940,7 +16940,7 @@
         <v>172</v>
       </c>
       <c r="AD174">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE174">
         <v>8000</v>
@@ -17032,7 +17032,7 @@
         <v>172</v>
       </c>
       <c r="AD175">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE175">
         <v>8000</v>
@@ -17124,7 +17124,7 @@
         <v>172</v>
       </c>
       <c r="AD176">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE176">
         <v>8000</v>
@@ -17216,7 +17216,7 @@
         <v>172</v>
       </c>
       <c r="AD177">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE177">
         <v>8000</v>
@@ -17308,7 +17308,7 @@
         <v>172</v>
       </c>
       <c r="AD178">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE178">
         <v>8000</v>
@@ -17406,7 +17406,7 @@
         <v>172</v>
       </c>
       <c r="AD179">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE179">
         <v>8000</v>
@@ -17504,7 +17504,7 @@
         <v>172</v>
       </c>
       <c r="AD180">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE180">
         <v>8000</v>
@@ -17596,7 +17596,7 @@
         <v>172</v>
       </c>
       <c r="AD181">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE181">
         <v>8000</v>
@@ -17688,7 +17688,7 @@
         <v>172</v>
       </c>
       <c r="AD182">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE182">
         <v>8000</v>
@@ -17780,7 +17780,7 @@
         <v>172</v>
       </c>
       <c r="AD183">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE183">
         <v>8000</v>
@@ -17872,7 +17872,7 @@
         <v>172</v>
       </c>
       <c r="AD184">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE184">
         <v>8000</v>
@@ -17964,7 +17964,7 @@
         <v>172</v>
       </c>
       <c r="AD185">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE185">
         <v>8000</v>
@@ -18056,7 +18056,7 @@
         <v>172</v>
       </c>
       <c r="AD186">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE186">
         <v>8000</v>
@@ -18148,7 +18148,7 @@
         <v>172</v>
       </c>
       <c r="AD187">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE187">
         <v>8000</v>
@@ -18240,7 +18240,7 @@
         <v>172</v>
       </c>
       <c r="AD188">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE188">
         <v>8000</v>
@@ -18332,7 +18332,7 @@
         <v>172</v>
       </c>
       <c r="AD189">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE189">
         <v>8000</v>
@@ -18424,7 +18424,7 @@
         <v>172</v>
       </c>
       <c r="AD190">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE190">
         <v>8000</v>
@@ -18516,7 +18516,7 @@
         <v>172</v>
       </c>
       <c r="AD191">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE191">
         <v>8000</v>
@@ -18608,7 +18608,7 @@
         <v>172</v>
       </c>
       <c r="AD192">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE192">
         <v>8000</v>
@@ -18697,7 +18697,7 @@
         <v>173</v>
       </c>
       <c r="AD193">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE193">
         <v>8000</v>
@@ -18786,7 +18786,7 @@
         <v>173</v>
       </c>
       <c r="AD194">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE194">
         <v>8000</v>
@@ -18875,7 +18875,7 @@
         <v>173</v>
       </c>
       <c r="AD195">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE195">
         <v>8000</v>
@@ -18964,7 +18964,7 @@
         <v>173</v>
       </c>
       <c r="AD196">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE196">
         <v>8000</v>
@@ -19062,7 +19062,7 @@
         <v>172</v>
       </c>
       <c r="AD197">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE197">
         <v>8000</v>
@@ -19160,7 +19160,7 @@
         <v>172</v>
       </c>
       <c r="AD198">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE198">
         <v>8000</v>
@@ -19252,7 +19252,7 @@
         <v>172</v>
       </c>
       <c r="AD199">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE199">
         <v>8000</v>
@@ -19344,7 +19344,7 @@
         <v>172</v>
       </c>
       <c r="AD200">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE200">
         <v>8000</v>
@@ -19436,7 +19436,7 @@
         <v>172</v>
       </c>
       <c r="AD201">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE201">
         <v>8000</v>
@@ -19525,7 +19525,7 @@
         <v>173</v>
       </c>
       <c r="AD202">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE202">
         <v>8000</v>
@@ -19617,7 +19617,7 @@
         <v>172</v>
       </c>
       <c r="AD203">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE203">
         <v>8000</v>
@@ -19706,7 +19706,7 @@
         <v>172</v>
       </c>
       <c r="AD204">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE204">
         <v>8000</v>
@@ -19795,7 +19795,7 @@
         <v>172</v>
       </c>
       <c r="AD205">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE205">
         <v>8000</v>
@@ -19884,7 +19884,7 @@
         <v>172</v>
       </c>
       <c r="AD206">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE206">
         <v>8000</v>
@@ -19973,7 +19973,7 @@
         <v>172</v>
       </c>
       <c r="AD207">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE207">
         <v>8000</v>
@@ -20065,7 +20065,7 @@
         <v>172</v>
       </c>
       <c r="AD208">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE208">
         <v>8000</v>
@@ -20154,7 +20154,7 @@
         <v>172</v>
       </c>
       <c r="AD209">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE209">
         <v>8000</v>
@@ -20243,7 +20243,7 @@
         <v>172</v>
       </c>
       <c r="AD210">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE210">
         <v>8000</v>
@@ -20338,7 +20338,7 @@
         <v>172</v>
       </c>
       <c r="AD211">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE211">
         <v>8000</v>
@@ -20433,7 +20433,7 @@
         <v>172</v>
       </c>
       <c r="AD212">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE212">
         <v>8000</v>
@@ -20522,7 +20522,7 @@
         <v>172</v>
       </c>
       <c r="AD213">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE213">
         <v>8000</v>
@@ -20611,7 +20611,7 @@
         <v>172</v>
       </c>
       <c r="AD214">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE214">
         <v>8000</v>
@@ -20700,7 +20700,7 @@
         <v>172</v>
       </c>
       <c r="AD215">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE215">
         <v>8000</v>
@@ -20789,7 +20789,7 @@
         <v>172</v>
       </c>
       <c r="AD216">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE216">
         <v>8000</v>
@@ -20878,7 +20878,7 @@
         <v>172</v>
       </c>
       <c r="AD217">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE217">
         <v>8000</v>
@@ -20967,7 +20967,7 @@
         <v>172</v>
       </c>
       <c r="AD218">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE218">
         <v>8000</v>
@@ -21062,7 +21062,7 @@
         <v>172</v>
       </c>
       <c r="AD219">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE219">
         <v>8000</v>
@@ -21157,7 +21157,7 @@
         <v>172</v>
       </c>
       <c r="AD220">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE220">
         <v>8000</v>
@@ -21246,7 +21246,7 @@
         <v>172</v>
       </c>
       <c r="AD221">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE221">
         <v>8000</v>
@@ -21335,7 +21335,7 @@
         <v>172</v>
       </c>
       <c r="AD222">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE222">
         <v>8000</v>
@@ -21424,7 +21424,7 @@
         <v>172</v>
       </c>
       <c r="AD223">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE223">
         <v>8000</v>
@@ -21513,7 +21513,7 @@
         <v>172</v>
       </c>
       <c r="AD224">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE224">
         <v>8000</v>
@@ -21602,7 +21602,7 @@
         <v>172</v>
       </c>
       <c r="AD225">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE225">
         <v>8000</v>
@@ -21691,7 +21691,7 @@
         <v>172</v>
       </c>
       <c r="AD226">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE226">
         <v>8000</v>
@@ -21780,7 +21780,7 @@
         <v>172</v>
       </c>
       <c r="AD227">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE227">
         <v>8000</v>
@@ -21875,7 +21875,7 @@
         <v>172</v>
       </c>
       <c r="AD228">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE228">
         <v>8000</v>
@@ -21970,7 +21970,7 @@
         <v>172</v>
       </c>
       <c r="AD229">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE229">
         <v>8000</v>
@@ -22059,7 +22059,7 @@
         <v>172</v>
       </c>
       <c r="AD230">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE230">
         <v>8000</v>
@@ -22148,7 +22148,7 @@
         <v>172</v>
       </c>
       <c r="AD231">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE231">
         <v>8000</v>
@@ -22237,7 +22237,7 @@
         <v>172</v>
       </c>
       <c r="AD232">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE232">
         <v>8000</v>
@@ -22326,7 +22326,7 @@
         <v>172</v>
       </c>
       <c r="AD233">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE233">
         <v>8000</v>
@@ -22415,7 +22415,7 @@
         <v>172</v>
       </c>
       <c r="AD234">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE234">
         <v>8000</v>
@@ -22504,7 +22504,7 @@
         <v>172</v>
       </c>
       <c r="AD235">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE235">
         <v>8000</v>
@@ -22593,7 +22593,7 @@
         <v>172</v>
       </c>
       <c r="AD236">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE236">
         <v>8000</v>
@@ -22682,7 +22682,7 @@
         <v>172</v>
       </c>
       <c r="AD237">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE237">
         <v>8000</v>
@@ -22771,7 +22771,7 @@
         <v>172</v>
       </c>
       <c r="AD238">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE238">
         <v>8000</v>
@@ -22860,7 +22860,7 @@
         <v>173</v>
       </c>
       <c r="AD239">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE239">
         <v>8000</v>
@@ -22955,7 +22955,7 @@
         <v>173</v>
       </c>
       <c r="AD240">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE240">
         <v>8000</v>
@@ -23050,7 +23050,7 @@
         <v>173</v>
       </c>
       <c r="AD241">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE241">
         <v>8000</v>
@@ -23139,7 +23139,7 @@
         <v>173</v>
       </c>
       <c r="AD242">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE242">
         <v>8000</v>
@@ -23228,7 +23228,7 @@
         <v>173</v>
       </c>
       <c r="AD243">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE243">
         <v>8000</v>
@@ -23317,7 +23317,7 @@
         <v>173</v>
       </c>
       <c r="AD244">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE244">
         <v>8000</v>
@@ -23403,7 +23403,7 @@
         <v>167.0191129130019</v>
       </c>
       <c r="AD245">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE245">
         <v>8000</v>
@@ -23489,7 +23489,7 @@
         <v>515.9000522871675</v>
       </c>
       <c r="AD246">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE246">
         <v>8000</v>
@@ -23581,7 +23581,7 @@
         <v>172</v>
       </c>
       <c r="AD247">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE247">
         <v>8000</v>
@@ -23673,7 +23673,7 @@
         <v>172</v>
       </c>
       <c r="AD248">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE248">
         <v>8000</v>
@@ -23765,7 +23765,7 @@
         <v>172</v>
       </c>
       <c r="AD249">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE249">
         <v>8000</v>
@@ -23857,7 +23857,7 @@
         <v>172</v>
       </c>
       <c r="AD250">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE250">
         <v>8000</v>
@@ -23946,7 +23946,7 @@
         <v>173</v>
       </c>
       <c r="AD251">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE251">
         <v>8000</v>
@@ -24035,7 +24035,7 @@
         <v>172</v>
       </c>
       <c r="AD252">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE252">
         <v>8000</v>
@@ -24124,7 +24124,7 @@
         <v>172</v>
       </c>
       <c r="AD253">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE253">
         <v>8000</v>
@@ -31995,7 +31995,7 @@
         <v>172</v>
       </c>
       <c r="AD338">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE338">
         <v>8000</v>
@@ -32090,7 +32090,7 @@
         <v>173</v>
       </c>
       <c r="AD339">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE339">
         <v>8000</v>
@@ -32185,7 +32185,7 @@
         <v>172</v>
       </c>
       <c r="AD340">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE340">
         <v>8000</v>
@@ -32274,7 +32274,7 @@
         <v>172</v>
       </c>
       <c r="AD341">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE341">
         <v>8000</v>
@@ -32363,7 +32363,7 @@
         <v>172</v>
       </c>
       <c r="AD342">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE342">
         <v>8000</v>
@@ -32458,7 +32458,7 @@
         <v>172</v>
       </c>
       <c r="AD343">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE343">
         <v>8000</v>
@@ -32553,7 +32553,7 @@
         <v>173</v>
       </c>
       <c r="AD344">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE344">
         <v>8000</v>
@@ -32642,7 +32642,7 @@
         <v>173</v>
       </c>
       <c r="AD345">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE345">
         <v>8000</v>
@@ -32737,7 +32737,7 @@
         <v>172</v>
       </c>
       <c r="AD346">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE346">
         <v>8000</v>
@@ -32832,7 +32832,7 @@
         <v>172</v>
       </c>
       <c r="AD347">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE347">
         <v>8000</v>
@@ -32921,7 +32921,7 @@
         <v>172</v>
       </c>
       <c r="AD348">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE348">
         <v>8000</v>
@@ -33010,7 +33010,7 @@
         <v>172</v>
       </c>
       <c r="AD349">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE349">
         <v>8000</v>
@@ -33105,7 +33105,7 @@
         <v>172</v>
       </c>
       <c r="AD350">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE350">
         <v>8000</v>
@@ -33194,7 +33194,7 @@
         <v>173</v>
       </c>
       <c r="AD351">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE351">
         <v>8000</v>
@@ -33292,7 +33292,7 @@
         <v>172</v>
       </c>
       <c r="AD352">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE352">
         <v>8000</v>
@@ -33381,7 +33381,7 @@
         <v>172</v>
       </c>
       <c r="AD353">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE353">
         <v>8000</v>
@@ -33479,7 +33479,7 @@
         <v>172</v>
       </c>
       <c r="AD354">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE354">
         <v>8000</v>
@@ -33571,7 +33571,7 @@
         <v>172</v>
       </c>
       <c r="AD355">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE355">
         <v>8000</v>
@@ -33663,7 +33663,7 @@
         <v>172</v>
       </c>
       <c r="AD356">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE356">
         <v>8000</v>
@@ -33752,7 +33752,7 @@
         <v>172</v>
       </c>
       <c r="AD357">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE357">
         <v>8000</v>
@@ -33850,7 +33850,7 @@
         <v>172</v>
       </c>
       <c r="AD358">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE358">
         <v>8000</v>
@@ -33948,7 +33948,7 @@
         <v>172</v>
       </c>
       <c r="AD359">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE359">
         <v>8000</v>
@@ -34040,7 +34040,7 @@
         <v>172</v>
       </c>
       <c r="AD360">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE360">
         <v>8000</v>
@@ -34132,7 +34132,7 @@
         <v>172</v>
       </c>
       <c r="AD361">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE361">
         <v>8000</v>
@@ -34230,7 +34230,7 @@
         <v>172</v>
       </c>
       <c r="AD362">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE362">
         <v>8000</v>
@@ -34328,7 +34328,7 @@
         <v>172</v>
       </c>
       <c r="AD363">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE363">
         <v>8000</v>
@@ -34429,7 +34429,7 @@
         <v>172</v>
       </c>
       <c r="AD364">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE364">
         <v>8000</v>
@@ -34521,7 +34521,7 @@
         <v>172</v>
       </c>
       <c r="AD365">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE365">
         <v>8000</v>
@@ -34613,7 +34613,7 @@
         <v>172</v>
       </c>
       <c r="AD366">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE366">
         <v>8000</v>
@@ -39599,7 +39599,7 @@
         <v>172</v>
       </c>
       <c r="AD420">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE420">
         <v>8000</v>
@@ -39694,7 +39694,7 @@
         <v>172</v>
       </c>
       <c r="AD421">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE421">
         <v>8000</v>
@@ -39789,7 +39789,7 @@
         <v>172</v>
       </c>
       <c r="AD422">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE422">
         <v>8000</v>
@@ -39878,7 +39878,7 @@
         <v>172</v>
       </c>
       <c r="AD423">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE423">
         <v>8000</v>
@@ -39976,7 +39976,7 @@
         <v>172</v>
       </c>
       <c r="AD424">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE424">
         <v>8000</v>
@@ -40065,7 +40065,7 @@
         <v>172</v>
       </c>
       <c r="AD425">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE425">
         <v>8000</v>
@@ -40160,7 +40160,7 @@
         <v>172</v>
       </c>
       <c r="AD426">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE426">
         <v>8000</v>
@@ -40255,7 +40255,7 @@
         <v>172</v>
       </c>
       <c r="AD427">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE427">
         <v>8000</v>
@@ -40344,7 +40344,7 @@
         <v>172</v>
       </c>
       <c r="AD428">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE428">
         <v>8000</v>
@@ -40439,7 +40439,7 @@
         <v>172</v>
       </c>
       <c r="AD429">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE429">
         <v>8000</v>
@@ -40534,7 +40534,7 @@
         <v>172</v>
       </c>
       <c r="AD430">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE430">
         <v>8000</v>
@@ -40635,7 +40635,7 @@
         <v>172</v>
       </c>
       <c r="AD431">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE431">
         <v>8000</v>
@@ -40730,7 +40730,7 @@
         <v>173</v>
       </c>
       <c r="AD432">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE432">
         <v>8000</v>
@@ -40819,7 +40819,7 @@
         <v>173</v>
       </c>
       <c r="AD433">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE433">
         <v>8000</v>
@@ -40908,7 +40908,7 @@
         <v>172</v>
       </c>
       <c r="AD434">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE434">
         <v>8000</v>
@@ -41003,7 +41003,7 @@
         <v>172</v>
       </c>
       <c r="AD435">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE435">
         <v>8000</v>
@@ -41101,7 +41101,7 @@
         <v>172</v>
       </c>
       <c r="AD436">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE436">
         <v>8000</v>
@@ -41193,7 +41193,7 @@
         <v>172</v>
       </c>
       <c r="AD437">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE437">
         <v>8000</v>
@@ -41291,7 +41291,7 @@
         <v>172</v>
       </c>
       <c r="AD438">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE438">
         <v>8000</v>
@@ -41383,7 +41383,7 @@
         <v>172</v>
       </c>
       <c r="AD439">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE439">
         <v>8000</v>
@@ -41481,7 +41481,7 @@
         <v>172</v>
       </c>
       <c r="AD440">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE440">
         <v>8000</v>
@@ -41579,7 +41579,7 @@
         <v>172</v>
       </c>
       <c r="AD441">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE441">
         <v>8000</v>
@@ -41671,7 +41671,7 @@
         <v>172</v>
       </c>
       <c r="AD442">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE442">
         <v>8000</v>
@@ -41769,7 +41769,7 @@
         <v>172</v>
       </c>
       <c r="AD443">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE443">
         <v>8000</v>
@@ -41861,7 +41861,7 @@
         <v>172</v>
       </c>
       <c r="AD444">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE444">
         <v>8000</v>
@@ -41956,7 +41956,7 @@
         <v>172</v>
       </c>
       <c r="AD445">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE445">
         <v>8000</v>
@@ -42051,7 +42051,7 @@
         <v>172</v>
       </c>
       <c r="AD446">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE446">
         <v>8000</v>
@@ -42146,7 +42146,7 @@
         <v>173</v>
       </c>
       <c r="AD447">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE447">
         <v>8000</v>
@@ -42235,7 +42235,7 @@
         <v>173</v>
       </c>
       <c r="AD448">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE448">
         <v>8000</v>
@@ -42330,7 +42330,7 @@
         <v>173</v>
       </c>
       <c r="AD449">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE449">
         <v>8000</v>
@@ -42416,7 +42416,7 @@
         <v>432.2405843487079</v>
       </c>
       <c r="AD450">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE450">
         <v>8000</v>
@@ -42505,7 +42505,7 @@
         <v>172</v>
       </c>
       <c r="AD451">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE451">
         <v>8000</v>
@@ -42591,7 +42591,7 @@
         <v>99.13392508384629</v>
       </c>
       <c r="AD452">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE452">
         <v>8000</v>
@@ -42683,7 +42683,7 @@
         <v>172</v>
       </c>
       <c r="AD453">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE453">
         <v>8000</v>
@@ -42772,7 +42772,7 @@
         <v>173</v>
       </c>
       <c r="AD454">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE454">
         <v>8000</v>
@@ -42861,7 +42861,7 @@
         <v>173</v>
       </c>
       <c r="AD455">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE455">
         <v>8000</v>
@@ -42950,7 +42950,7 @@
         <v>173</v>
       </c>
       <c r="AD456">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE456">
         <v>8000</v>
@@ -43039,7 +43039,7 @@
         <v>172</v>
       </c>
       <c r="AD457">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE457">
         <v>8000</v>
@@ -43128,7 +43128,7 @@
         <v>172</v>
       </c>
       <c r="AD458">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE458">
         <v>8000</v>
@@ -43220,7 +43220,7 @@
         <v>172</v>
       </c>
       <c r="AD459">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE459">
         <v>8000</v>
@@ -43312,7 +43312,7 @@
         <v>172</v>
       </c>
       <c r="AD460">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE460">
         <v>8000</v>
@@ -43401,7 +43401,7 @@
         <v>172</v>
       </c>
       <c r="AD461">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE461">
         <v>8000</v>
@@ -43490,7 +43490,7 @@
         <v>172</v>
       </c>
       <c r="AD462">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE462">
         <v>8000</v>
@@ -43579,7 +43579,7 @@
         <v>172</v>
       </c>
       <c r="AD463">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE463">
         <v>8000</v>
@@ -43668,7 +43668,7 @@
         <v>172</v>
       </c>
       <c r="AD464">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE464">
         <v>8000</v>
@@ -43760,7 +43760,7 @@
         <v>172</v>
       </c>
       <c r="AD465">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE465">
         <v>8000</v>
@@ -43852,7 +43852,7 @@
         <v>172</v>
       </c>
       <c r="AD466">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE466">
         <v>8000</v>
@@ -43941,7 +43941,7 @@
         <v>172</v>
       </c>
       <c r="AD467">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE467">
         <v>8000</v>
@@ -44033,7 +44033,7 @@
         <v>172</v>
       </c>
       <c r="AD468">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE468">
         <v>8000</v>
@@ -44134,7 +44134,7 @@
         <v>172</v>
       </c>
       <c r="AD469">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE469">
         <v>8000</v>
@@ -44223,7 +44223,7 @@
         <v>172</v>
       </c>
       <c r="AD470">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE470">
         <v>8000</v>
@@ -44312,7 +44312,7 @@
         <v>172</v>
       </c>
       <c r="AD471">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE471">
         <v>8000</v>
@@ -44413,7 +44413,7 @@
         <v>172</v>
       </c>
       <c r="AD472">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE472">
         <v>8000</v>
@@ -50800,7 +50800,7 @@
         <v>173</v>
       </c>
       <c r="AD541">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE541">
         <v>8000</v>
@@ -50892,7 +50892,7 @@
         <v>172</v>
       </c>
       <c r="AD542">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE542">
         <v>8000</v>
@@ -50987,7 +50987,7 @@
         <v>172</v>
       </c>
       <c r="AD543">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE543">
         <v>8000</v>
@@ -51076,7 +51076,7 @@
         <v>172</v>
       </c>
       <c r="AD544">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE544">
         <v>8000</v>
@@ -51165,7 +51165,7 @@
         <v>172</v>
       </c>
       <c r="AD545">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE545">
         <v>8000</v>
@@ -51254,7 +51254,7 @@
         <v>172</v>
       </c>
       <c r="AD546">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE546">
         <v>8000</v>
@@ -51343,7 +51343,7 @@
         <v>172</v>
       </c>
       <c r="AD547">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE547">
         <v>8000</v>
@@ -51432,7 +51432,7 @@
         <v>172</v>
       </c>
       <c r="AD548">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE548">
         <v>8000</v>
@@ -51524,7 +51524,7 @@
         <v>172</v>
       </c>
       <c r="AD549">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE549">
         <v>8000</v>
@@ -51619,7 +51619,7 @@
         <v>172</v>
       </c>
       <c r="AD550">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE550">
         <v>8000</v>
@@ -51714,7 +51714,7 @@
         <v>172</v>
       </c>
       <c r="AD551">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE551">
         <v>8000</v>
@@ -51809,7 +51809,7 @@
         <v>172</v>
       </c>
       <c r="AD552">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE552">
         <v>8000</v>
@@ -51904,7 +51904,7 @@
         <v>172</v>
       </c>
       <c r="AD553">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE553">
         <v>8000</v>
@@ -51999,7 +51999,7 @@
         <v>172</v>
       </c>
       <c r="AD554">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE554">
         <v>8000</v>
@@ -52088,7 +52088,7 @@
         <v>172</v>
       </c>
       <c r="AD555">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE555">
         <v>8000</v>
@@ -52177,7 +52177,7 @@
         <v>172</v>
       </c>
       <c r="AD556">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE556">
         <v>8000</v>
@@ -52266,7 +52266,7 @@
         <v>172</v>
       </c>
       <c r="AD557">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE557">
         <v>8000</v>
@@ -52355,7 +52355,7 @@
         <v>172</v>
       </c>
       <c r="AD558">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE558">
         <v>8000</v>
@@ -52444,7 +52444,7 @@
         <v>172</v>
       </c>
       <c r="AD559">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE559">
         <v>8000</v>
@@ -52533,7 +52533,7 @@
         <v>172</v>
       </c>
       <c r="AD560">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE560">
         <v>8000</v>
@@ -52622,7 +52622,7 @@
         <v>172</v>
       </c>
       <c r="AD561">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE561">
         <v>8000</v>
@@ -52711,7 +52711,7 @@
         <v>172</v>
       </c>
       <c r="AD562">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE562">
         <v>8000</v>
@@ -52806,7 +52806,7 @@
         <v>172</v>
       </c>
       <c r="AD563">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE563">
         <v>8000</v>
@@ -52901,7 +52901,7 @@
         <v>172</v>
       </c>
       <c r="AD564">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE564">
         <v>8000</v>
@@ -52996,7 +52996,7 @@
         <v>172</v>
       </c>
       <c r="AD565">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE565">
         <v>8000</v>
@@ -53085,7 +53085,7 @@
         <v>172</v>
       </c>
       <c r="AD566">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE566">
         <v>8000</v>
@@ -53174,7 +53174,7 @@
         <v>172</v>
       </c>
       <c r="AD567">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE567">
         <v>8000</v>
@@ -53266,7 +53266,7 @@
         <v>172</v>
       </c>
       <c r="AD568">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE568">
         <v>8000</v>
@@ -53358,7 +53358,7 @@
         <v>172</v>
       </c>
       <c r="AD569">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE569">
         <v>8000</v>
@@ -53450,7 +53450,7 @@
         <v>172</v>
       </c>
       <c r="AD570">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE570">
         <v>8000</v>
@@ -53542,7 +53542,7 @@
         <v>172</v>
       </c>
       <c r="AD571">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE571">
         <v>8000</v>
@@ -53634,7 +53634,7 @@
         <v>172</v>
       </c>
       <c r="AD572">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE572">
         <v>8000</v>
@@ -53732,7 +53732,7 @@
         <v>172</v>
       </c>
       <c r="AD573">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE573">
         <v>8000</v>
@@ -53821,7 +53821,7 @@
         <v>173</v>
       </c>
       <c r="AD574">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE574">
         <v>8000</v>
@@ -53913,7 +53913,7 @@
         <v>172</v>
       </c>
       <c r="AD575">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE575">
         <v>8000</v>
@@ -54002,7 +54002,7 @@
         <v>173</v>
       </c>
       <c r="AD576">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE576">
         <v>8000</v>
@@ -54091,7 +54091,7 @@
         <v>173</v>
       </c>
       <c r="AD577">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE577">
         <v>8000</v>
@@ -54180,7 +54180,7 @@
         <v>173</v>
       </c>
       <c r="AD578">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE578">
         <v>8000</v>
@@ -54269,7 +54269,7 @@
         <v>173</v>
       </c>
       <c r="AD579">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE579">
         <v>8000</v>
@@ -54364,7 +54364,7 @@
         <v>173</v>
       </c>
       <c r="AD580">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE580">
         <v>8000</v>
@@ -54462,7 +54462,7 @@
         <v>172</v>
       </c>
       <c r="AD581">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE581">
         <v>8000</v>
@@ -54560,7 +54560,7 @@
         <v>172</v>
       </c>
       <c r="AD582">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE582">
         <v>8000</v>
@@ -54649,7 +54649,7 @@
         <v>173</v>
       </c>
       <c r="AD583">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE583">
         <v>8000</v>
@@ -54741,7 +54741,7 @@
         <v>172</v>
       </c>
       <c r="AD584">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE584">
         <v>8000</v>
@@ -54833,7 +54833,7 @@
         <v>172</v>
       </c>
       <c r="AD585">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE585">
         <v>8000</v>
@@ -54925,7 +54925,7 @@
         <v>172</v>
       </c>
       <c r="AD586">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE586">
         <v>8000</v>
@@ -55014,7 +55014,7 @@
         <v>172</v>
       </c>
       <c r="AD587">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE587">
         <v>8000</v>
@@ -55103,7 +55103,7 @@
         <v>172</v>
       </c>
       <c r="AD588">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE588">
         <v>8000</v>
@@ -55195,7 +55195,7 @@
         <v>172</v>
       </c>
       <c r="AD589">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE589">
         <v>8000</v>
@@ -55287,7 +55287,7 @@
         <v>172</v>
       </c>
       <c r="AD590">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE590">
         <v>8000</v>
@@ -55382,7 +55382,7 @@
         <v>173</v>
       </c>
       <c r="AD591">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE591">
         <v>8000</v>
@@ -55480,7 +55480,7 @@
         <v>172</v>
       </c>
       <c r="AD592">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE592">
         <v>8000</v>
@@ -55578,7 +55578,7 @@
         <v>172</v>
       </c>
       <c r="AD593">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE593">
         <v>8000</v>
@@ -55670,7 +55670,7 @@
         <v>172</v>
       </c>
       <c r="AD594">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE594">
         <v>8000</v>
@@ -55762,7 +55762,7 @@
         <v>172</v>
       </c>
       <c r="AD595">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE595">
         <v>8000</v>
@@ -55854,7 +55854,7 @@
         <v>172</v>
       </c>
       <c r="AD596">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE596">
         <v>8000</v>
@@ -55946,7 +55946,7 @@
         <v>172</v>
       </c>
       <c r="AD597">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE597">
         <v>8000</v>
@@ -56044,7 +56044,7 @@
         <v>172</v>
       </c>
       <c r="AD598">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE598">
         <v>8000</v>
@@ -56142,7 +56142,7 @@
         <v>172</v>
       </c>
       <c r="AD599">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE599">
         <v>8000</v>
@@ -56240,7 +56240,7 @@
         <v>172</v>
       </c>
       <c r="AD600">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE600">
         <v>8000</v>
@@ -56332,7 +56332,7 @@
         <v>172</v>
       </c>
       <c r="AD601">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE601">
         <v>8000</v>
@@ -56421,7 +56421,7 @@
         <v>172</v>
       </c>
       <c r="AD602">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE602">
         <v>8000</v>
@@ -56519,7 +56519,7 @@
         <v>172</v>
       </c>
       <c r="AD603">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE603">
         <v>8000</v>
